--- a/PO_TBD_20260606.xlsx
+++ b/PO_TBD_20260606.xlsx
@@ -5110,7 +5110,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-06 03:26</t>
+          <t>Generated: 2026-06-06 08:03</t>
         </is>
       </c>
     </row>

--- a/PO_TBD_20260606.xlsx
+++ b/PO_TBD_20260606.xlsx
@@ -5110,7 +5110,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-06 08:03</t>
+          <t>Generated: 2026-06-06 08:52</t>
         </is>
       </c>
     </row>

--- a/PO_TBD_20260606.xlsx
+++ b/PO_TBD_20260606.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
+          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1849,13 +1849,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
+          <t>TAB EUTHYROX (LEVOTHYROXINE SODIUM) 100MCG MERCK</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -1874,20 +1874,20 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>97</v>
+        <v>0.527</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>97</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="50">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>TAB EUTHYROX (LEVOTHYROXINE SODIUM) 100MCG MERCK</t>
+          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1906,20 +1906,20 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.527</v>
+        <v>106.5</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>105.4</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="51">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
+          <t>NASONEX AQUEOUS NASAL SPRAY 0.05% 60D (MOMETASONE FUROATE) SCENT-FREE ORGANON HEIST BV</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E51" s="8" t="n">
@@ -1948,10 +1948,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>106.5</v>
+        <v>0</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>106.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>NASONEX AQUEOUS NASAL SPRAY 0.05% 60D (MOMETASONE FUROATE) SCENT-FREE ORGANON HEIST BV</t>
+          <t>TAB EXFORGE 5/80 (AMLODIPINE 5MG/ VALSARTAN 80MG) NORVATIS</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -1970,20 +1970,20 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>0</v>
+        <v>2.00821</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>0</v>
+        <v>84.34</v>
       </c>
     </row>
     <row r="53">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>TAB EXFORGE 5/80 (AMLODIPINE 5MG/ VALSARTAN 80MG) NORVATIS</t>
+          <t>TAB ROSUVASTATIN 20MG SYNERRV</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2009,13 +2009,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>2.00821</v>
+        <v>0</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>84.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>TAB ROSUVASTATIN 20MG SYNERRV</t>
+          <t>TAB ATORVASTATIN 20MG SYNERRV</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>TAB ATORVASTATIN 20MG SYNERRV</t>
+          <t>TAB ZIOMYCIN (AZITHROMYCIN) 500MG SYNERRV</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>TAB ZIOMYCIN (AZITHROMYCIN) 500MG SYNERRV</t>
+          <t>TAB ZIOMYCIN (AZITHROMYCIN) 250MG SYNERRV</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>TAB ZIOMYCIN (AZITHROMYCIN) 250MG SYNERRV</t>
+          <t>TAB GLIT (PIOGLITAZONE) 30MG SYNERRV</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>TAB GLIT (PIOGLITAZONE) 30MG SYNERRV</t>
+          <t>TAB GLIT (PIOGLITAZONE) 15MG SYNERRV</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>TAB GLIT (PIOGLITAZONE) 15MG SYNERRV</t>
+          <t>DYNA CALAMINE LOTION (CALAMINE POWDER 15% W/V / MENTHOL 0.15% W/V) 100ML DYNAPHARM (M)</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -2194,20 +2194,20 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>0</v>
+        <v>6.36667</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>0</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="60">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>DYNA CALAMINE LOTION (CALAMINE POWDER 15% W/V / MENTHOL 0.15% W/V) 100ML DYNAPHARM (M)</t>
+          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2226,20 +2226,20 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>AMPULE</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>6.36667</v>
+        <v>1.5</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>12.73</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
+          <t>TAB ZITHROMAX (AZITHROMYCIN) 250MG 6'S PFIZER</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -2258,20 +2258,20 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>1.5</v>
+        <v>42.4</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>6</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="62">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>TAB ZITHROMAX (AZITHROMYCIN) 250MG 6'S PFIZER</t>
+          <t>CANDAZOLE LOTION (CLOTRIMAZOLE 1% W/W) 10ML HOE</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
@@ -2300,10 +2300,10 @@
         <v>3</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>42.4</v>
+        <v>12.5</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>127.2</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="63">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>CANDAZOLE LOTION (CLOTRIMAZOLE 1% W/W) 10ML HOE</t>
+          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>12.5</v>
+        <v>0.08</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>37.5</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="64">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
+          <t>TAB NEXIUM MUPS (ESOMEPRAZOLE) 40MG ASTRAZENECA</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2358,16 +2358,16 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0.08</v>
+        <v>6.77857</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>3.44</v>
+        <v>210.14</v>
       </c>
     </row>
     <row r="65">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>TAB NEXIUM MUPS (ESOMEPRAZOLE) 40MG ASTRAZENECA</t>
+          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -2386,20 +2386,20 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>6.77857</v>
+        <v>5.9</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>210.14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
+          <t>TAB BELTAS (BILASTINE) 20MG GLENMARK</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -2418,20 +2418,20 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>5.9</v>
+        <v>0.798</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>59</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="67">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>TAB BELTAS (BILASTINE) 20MG GLENMARK</t>
+          <t>TAB PARACAP 500MG HEALTH PHARM</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -2454,16 +2454,16 @@
         </is>
       </c>
       <c r="E67" s="8" t="n">
-        <v>30</v>
+        <v>390</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>85</v>
+        <v>256</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>0.798</v>
+        <v>0.157</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>67.83</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="68">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>TAB PARACAP 500MG HEALTH PHARM</t>
+          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>390</v>
+        <v>60</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>256</v>
+        <v>117</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>0.157</v>
+        <v>0.459</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>40.19</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="69">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
+          <t>TAB SPASIL (DIPHENOXYLATE 2.5MG/ATROPINE 0.025MG) IMEKS</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -2518,16 +2518,16 @@
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>117</v>
+        <v>209</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>0.459</v>
+        <v>0.164</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>53.7</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="70">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>TAB SPASIL (DIPHENOXYLATE 2.5MG/ATROPINE 0.025MG) IMEKS</t>
+          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>400</v>
+        <v>210</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>209</v>
+        <v>157</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>0.164</v>
+        <v>1.814</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>34.28</v>
+        <v>284.8</v>
       </c>
     </row>
     <row r="71">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
+          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="E71" s="8" t="n">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>1.814</v>
+        <v>0.089</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>284.8</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="72">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
+          <t>TAB NORCOLUT (NORETHISTERONE) 5MG PAHANG PHARMACY</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -2614,16 +2614,16 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>0.089</v>
+        <v>0.5</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>7.83</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>TAB NORCOLUT (NORETHISTERONE) 5MG PAHANG PHARMACY</t>
+          <t>TAB VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E73" s="8" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>0.5</v>
+        <v>0.119</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="74">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>TAB VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
+          <t>TAB IBUPROFEN 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -2681,13 +2681,13 @@
         <v>90</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>0.119</v>
+        <v>0.203</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>3.45</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="75">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>TAB IBUPROFEN 400MG Y.S.P.</t>
+          <t>TAB DUOFOLIC (FOLIC ACID) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -2710,16 +2710,16 @@
         </is>
       </c>
       <c r="E75" s="8" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>0.203</v>
+        <v>0.065</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.11</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="76">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>TAB DUOFOLIC (FOLIC ACID) 5MG DUOPHARMA</t>
+          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -2742,16 +2742,16 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>0.065</v>
+        <v>0.584</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>1.62</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="77">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
+          <t>CAP LOMODIUM (LOPERAMIDE) 2MG DYNAPHARM</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -2774,16 +2774,16 @@
         </is>
       </c>
       <c r="E77" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>0.584</v>
+        <v>0.093</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>23.36</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="78">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>CAP LOMODIUM (LOPERAMIDE) 2MG DYNAPHARM</t>
+          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -2802,20 +2802,20 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
+          <t>TAB DUPHASTON (DYDROGESTERONE) 10MG ABBOTT</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -2834,20 +2834,20 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E79" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F79" s="8" t="n">
         <v>16</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>0</v>
+        <v>3.675</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>0</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="80">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>TAB DUPHASTON (DYDROGESTERONE) 10MG ABBOTT</t>
+          <t>TAB HOVASC (AMLODIPINE) 5MG HOVID</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>3.675</v>
+        <v>0.24</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>58.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="81">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>TAB HOVASC (AMLODIPINE) 5MG HOVID</t>
+          <t>TAB HOVASC (AMLODIPINE) 10MG HOVID</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -2902,16 +2902,16 @@
         </is>
       </c>
       <c r="E81" s="8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="82">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>TAB HOVASC (AMLODIPINE) 10MG HOVID</t>
+          <t>TAB NORMATEN (ATENOLOL) 50MG XEPA</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0.35</v>
+        <v>0.26786</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="83">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>TAB NORMATEN (ATENOLOL) 50MG XEPA</t>
+          <t>TAB DELTACARBON (CHARCOAL) 250MG IMEKS</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="E83" s="8" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G83" s="10" t="n">
-        <v>0.26786</v>
+        <v>0.438</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>3.75</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="84">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>TAB DELTACARBON (CHARCOAL) 250MG IMEKS</t>
+          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -2998,16 +2998,16 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>15</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>0.438</v>
+        <v>1.617</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>6.57</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="85">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
+          <t>TAB COPASTIN (CLOPERASTINE) 10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -3030,16 +3030,16 @@
         </is>
       </c>
       <c r="E85" s="8" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>1.617</v>
+        <v>0.236</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>24.25</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="86">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>TAB COPASTIN (CLOPERASTINE) 10MG Y.S.P.</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -3062,16 +3062,16 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>0.236</v>
+        <v>1.53</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>5.9</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="87">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
+          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -3090,20 +3090,20 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E87" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>15.3</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="88">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
+          <t>IVD N/S 0.9% 500ML B. BRAUN</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3122,20 +3122,20 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>12</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>1.66</v>
+        <v>3.628</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>19.92</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="89">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>IVD N/S 0.9% 500ML B. BRAUN</t>
+          <t>TAB CAFFOX ( ERGOTAMINE TARTRATE 1MG + CAFFINE 100MG ) IMEKS</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -3154,20 +3154,20 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E89" s="8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>3.628</v>
+        <v>0.73</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>43.54</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="90">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>TAB CAFFOX ( ERGOTAMINE TARTRATE 1MG + CAFFINE 100MG ) IMEKS</t>
+          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3190,16 +3190,16 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>14</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>10.22</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="91">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
+          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -3222,16 +3222,16 @@
         </is>
       </c>
       <c r="E91" s="8" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>1.06</v>
+        <v>0.232</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>14.84</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="92">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
+          <t>EFF GRANULES AVOSODA (SODIUM BICARBONATE) 1.916G/SACHET ABIO</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -3250,20 +3250,20 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>0.232</v>
+        <v>1.01</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>5.8</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="93">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>EFF GRANULES AVOSODA (SODIUM BICARBONATE) 1.916G/SACHET ABIO</t>
+          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -3282,20 +3282,20 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E93" s="8" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>1.01</v>
+        <v>0.78</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>49.49</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="94">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
+          <t>TAB DULCOLAX ( BISACODYL ) 5MG SANOFI</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -3321,13 +3321,13 @@
         <v>20</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>0.78</v>
+        <v>0.265</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>10.14</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="95">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>TAB DULCOLAX ( BISACODYL ) 5MG SANOFI</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -3353,13 +3353,13 @@
         <v>20</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>0.265</v>
+        <v>0.68</v>
       </c>
       <c r="H95" s="10" t="n">
-        <v>3.98</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="96">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -3382,16 +3382,16 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>0.68</v>
+        <v>1.44</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>27.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="97">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
+          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -3410,20 +3410,20 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E97" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G97" s="10" t="n">
-        <v>1.44</v>
+        <v>5.5</v>
       </c>
       <c r="H97" s="10" t="n">
-        <v>14.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
+          <t>INJ PIRIMAT (CHLORPHENIRAMINE) 10MG/ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -3442,20 +3442,20 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>22</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="99">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>INJ PIRIMAT (CHLORPHENIRAMINE) 10MG/ML DUOPHARMA</t>
+          <t>NEBULE VENTOLIN (SALBUTAMOL) 2.5MG/2.5ML GSK</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -3474,20 +3474,20 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>RESPULE</t>
         </is>
       </c>
       <c r="E99" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F99" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G99" s="10" t="n">
-        <v>1.75</v>
+        <v>4.82</v>
       </c>
       <c r="H99" s="10" t="n">
-        <v>15.75</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="100">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>NEBULE VENTOLIN (SALBUTAMOL) 2.5MG/2.5ML GSK</t>
+          <t>SYR RETORIN (ERYTHROMYCIN) 200MG/5ML 60ML SM PHARMA</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -3506,20 +3506,20 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>RESPULE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>4.82</v>
+        <v>4</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>24.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>SYR RETORIN (ERYTHROMYCIN) 200MG/5ML 60ML SM PHARMA</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -3538,20 +3538,20 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E101" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>4</v>
+        <v>1.66</v>
       </c>
       <c r="H101" s="10" t="n">
-        <v>36</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="102">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>6.64</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="103">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>SUPP VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
+          <t>CAP BIOZOLE (FLUCANAZOLE) 150MG MEDISPEC</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
@@ -3602,20 +3602,20 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E103" s="8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>1.59</v>
+        <v>4.91</v>
       </c>
       <c r="H103" s="10" t="n">
-        <v>1.59</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="104">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>CAP BIOZOLE (FLUCANAZOLE) 150MG MEDISPEC</t>
+          <t>CANDID-B ( CLOTRIMAZOLE 1%W/W /BECLOMETHASONE 0.025%W/W ) CREAM 15G Y.S.P.</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -3634,20 +3634,20 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>4.91</v>
+        <v>12.33</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>24.55</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="105">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>CANDID-B ( CLOTRIMAZOLE 1%W/W /BECLOMETHASONE 0.025%W/W ) CREAM 15G Y.S.P.</t>
+          <t>CANDID EARDROPS (CLOTRIMAZOLE 1%) 15ML GLENMARK</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -3666,20 +3666,20 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F105" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="10" t="n">
-        <v>12.33</v>
+        <v>18.95</v>
       </c>
       <c r="H105" s="10" t="n">
-        <v>12.33</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="106">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>CANDID EARDROPS (CLOTRIMAZOLE 1%) 15ML GLENMARK</t>
+          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -3698,20 +3698,20 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>18.95</v>
+        <v>6.8</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>18.95</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="107">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
+          <t>SYR LACTUL (LACTULOSE 670MG/ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -3730,20 +3730,20 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E107" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G107" s="10" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="H107" s="10" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>SYR LACTUL (LACTULOSE 670MG/ML) 100ML Y.S.P.</t>
+          <t>SYR COLIMIX (DICYCLOMINE 5MG/ SIMETHICONE 50MG) 90ML XEPA</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -3766,16 +3766,16 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F108" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>10</v>
+        <v>7.55</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>20</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="109">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>SYR COLIMIX (DICYCLOMINE 5MG/ SIMETHICONE 50MG) 90ML XEPA</t>
+          <t>MDI VENTOLIN EVOHALER (SALBUTAMOL 100MCG) GSK</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -3794,20 +3794,20 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E109" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F109" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G109" s="10" t="n">
-        <v>7.55</v>
+        <v>26.1</v>
       </c>
       <c r="H109" s="10" t="n">
-        <v>15.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="110">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>MDI VENTOLIN EVOHALER (SALBUTAMOL 100MCG) GSK</t>
+          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -3826,20 +3826,20 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>26.1</v>
+        <v>8.15</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>52.2</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="111">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
+          <t>SYR FUCON (HYOSCINE-N-BUTYLBROMIDE) 1MG/ML 60ML Y.S.P.</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
@@ -3858,20 +3858,20 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E111" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G111" s="10" t="n">
-        <v>8.15</v>
+        <v>7.05</v>
       </c>
       <c r="H111" s="10" t="n">
-        <v>32.6</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="112">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>SYR FUCON (HYOSCINE-N-BUTYLBROMIDE) 1MG/ML 60ML Y.S.P.</t>
+          <t>NASAL DROPS ILIADIN 0.01% (OXYMETHAZOLINE) DECONGESTANT (&lt; 12MTHS ) P&amp;G</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -3900,10 +3900,10 @@
         <v>2</v>
       </c>
       <c r="G112" s="7" t="n">
-        <v>7.05</v>
+        <v>16.56</v>
       </c>
       <c r="H112" s="7" t="n">
-        <v>14.1</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="113">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>NASAL DROPS ILIADIN 0.01% (OXYMETHAZOLINE) DECONGESTANT (&lt; 12MTHS ) P&amp;G</t>
+          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
@@ -3926,16 +3926,16 @@
         </is>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G113" s="10" t="n">
-        <v>16.56</v>
+        <v>32</v>
       </c>
       <c r="H113" s="10" t="n">
-        <v>33.12</v>
+        <v>192</v>
       </c>
     </row>
     <row r="114">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
+          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -3958,16 +3958,16 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>192</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
+          <t>INJ NON-PREG (MEDROXYPROGESTERONE ACETATE IM 150MG/3ML) VIAL HEALOL PHARMA</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
@@ -3986,20 +3986,20 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E115" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G115" s="10" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H115" s="10" t="n">
-        <v>25</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>INJ NON-PREG (MEDROXYPROGESTERONE ACETATE IM 150MG/3ML) VIAL HEALOL PHARMA</t>
+          <t>TAB ESCAPELLE (LEVONORGESTREL) 1.5MG 1'S PAHANG PHARMACY</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -4018,20 +4018,20 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F116" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F116" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="G116" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="H116" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>TAB ESCAPELLE (LEVONORGESTREL) 1.5MG 1'S PAHANG PHARMACY</t>
+          <t>TAB SYNFLEX (NAPROXEN SODIUM) 550MG DKSH</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -4054,16 +4054,16 @@
         </is>
       </c>
       <c r="E117" s="8" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>12.5</v>
+        <v>1.414</v>
       </c>
       <c r="H117" s="10" t="n">
-        <v>25</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="118">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>TAB SYNFLEX (NAPROXEN SODIUM) 550MG DKSH</t>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -4082,20 +4082,20 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>1.414</v>
+        <v>5.5</v>
       </c>
       <c r="H118" s="7" t="n">
-        <v>7.07</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="119">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+          <t>VOREN (DICLOFENAC SODIUM 1%W/W) GEL PLUS 20G Y.SP.</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
@@ -4114,20 +4114,20 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E119" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F119" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G119" s="10" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="H119" s="10" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>VOREN (DICLOFENAC SODIUM 1%W/W) GEL PLUS 20G Y.SP.</t>
+          <t>FLANIL (METHYL SALICYLATE 10.20%, W/W, EUGENOL 1.36% W/W, MENTHOL 5.44% W/W) CREAM 30G MEDISPEC</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -4150,16 +4150,16 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>27</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="121">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>FLANIL (METHYL SALICYLATE 10.20%, W/W, EUGENOL 1.36% W/W, MENTHOL 5.44% W/W) CREAM 30G MEDISPEC</t>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
@@ -4178,20 +4178,20 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E121" s="8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G121" s="10" t="n">
-        <v>7.9</v>
+        <v>9.65</v>
       </c>
       <c r="H121" s="10" t="n">
-        <v>39.5</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="122">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
+          <t>CHAMPS D-WORMS SUSPENSION (ALBENDAZOLE 200MG/5ML) 10ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -4210,20 +4210,20 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>9.65</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H122" s="7" t="n">
-        <v>19.3</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>CHAMPS D-WORMS SUSPENSION (ALBENDAZOLE 200MG/5ML) 10ML DUOPHARMA</t>
+          <t>TAB DAFLON (DIOSMIN 900MG, HESPERIDIN 100MG) 1000MG SERVIER</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
@@ -4242,20 +4242,20 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E123" s="8" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G123" s="10" t="n">
-        <v>9.449999999999999</v>
+        <v>2.93</v>
       </c>
       <c r="H123" s="10" t="n">
-        <v>9.449999999999999</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="124">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>TAB DAFLON (DIOSMIN 900MG, HESPERIDIN 100MG) 1000MG SERVIER</t>
+          <t>FOBAN CREAM (FUSIDIC ACID 2% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -4274,20 +4274,20 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>2.93</v>
+        <v>14.3</v>
       </c>
       <c r="H124" s="7" t="n">
-        <v>14.65</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="125">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>FOBAN CREAM (FUSIDIC ACID 2% W/W) 15G HOE</t>
+          <t>PROCTOSEDYL OINTMENT (FRAMYCETIN SULPHATE 1% W/W, HYDROCORTISONE 0.5% W/W, CINCHOCAINE.5% W/W, AESCULIN 1% W/W) 15G ZUELLIG PHARMA</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="E125" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="10" t="n">
-        <v>14.3</v>
+        <v>35</v>
       </c>
       <c r="H125" s="10" t="n">
-        <v>14.3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="126">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>PROCTOSEDYL OINTMENT (FRAMYCETIN SULPHATE 1% W/W, HYDROCORTISONE 0.5% W/W, CINCHOCAINE.5% W/W, AESCULIN 1% W/W) 15G ZUELLIG PHARMA</t>
+          <t>CREAM MOMATE (MOMETASONE 0.1% W/W) 15G GLENMARK</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -4342,16 +4342,16 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>35</v>
+        <v>8.9</v>
       </c>
       <c r="H126" s="7" t="n">
-        <v>35</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="127">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>CREAM MOMATE (MOMETASONE 0.1% W/W) 15G GLENMARK</t>
+          <t>ELLGY CORNS &amp; WARTS  (SALICYLIC ACID 17% W/V) 10ML HOE</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
@@ -4374,16 +4374,16 @@
         </is>
       </c>
       <c r="E127" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F127" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F127" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="G127" s="10" t="n">
-        <v>8.9</v>
+        <v>14.93</v>
       </c>
       <c r="H127" s="10" t="n">
-        <v>26.7</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="128">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>ELLGY CORNS &amp; WARTS  (SALICYLIC ACID 17% W/V) 10ML HOE</t>
+          <t>FOBANCORT CREAM (FUSIDIC ACID 2% W/W, BETAMETHASONE 0.05% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -4406,16 +4406,16 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>14.93</v>
+        <v>14.3</v>
       </c>
       <c r="H128" s="7" t="n">
-        <v>29.86</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="129">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>FOBANCORT CREAM (FUSIDIC ACID 2% W/W, BETAMETHASONE 0.05% W/W) 15G HOE</t>
+          <t>INJ LARTIL (PROCHLORPERAZINE MESYLATE)12.5MG/ML 1ML VIAL DUOPHARMA</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
@@ -4434,20 +4434,20 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E129" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F129" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F129" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="G129" s="10" t="n">
-        <v>14.3</v>
+        <v>3.48</v>
       </c>
       <c r="H129" s="10" t="n">
-        <v>14.3</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="130">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>INJ LARTIL (PROCHLORPERAZINE MESYLATE)12.5MG/ML 1ML VIAL DUOPHARMA</t>
+          <t>CERUMOL EAR WAX SOFTNER DROPS 10ML</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -4476,10 +4476,10 @@
         <v>2</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>3.48</v>
+        <v>15</v>
       </c>
       <c r="H130" s="7" t="n">
-        <v>6.96</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>CERUMOL EAR WAX SOFTNER DROPS 10ML</t>
+          <t>CIPMAX (CIPROFLOXACIN 0.3%) EYE DROPS 5ML SAMCHUNDANG</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
@@ -4505,13 +4505,13 @@
         <v>8</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G131" s="10" t="n">
-        <v>15</v>
+        <v>9.5</v>
       </c>
       <c r="H131" s="10" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="132">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>CIPMAX (CIPROFLOXACIN 0.3%) EYE DROPS 5ML SAMCHUNDANG</t>
+          <t>CANDACORT CREAM (CLOTRIMAZOLE 1% / HYDROCORTISONE 1% ) 15G HOE</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -4530,20 +4530,20 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>9.5</v>
+        <v>8.15</v>
       </c>
       <c r="H132" s="7" t="n">
-        <v>38</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="133">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>CANDACORT CREAM (CLOTRIMAZOLE 1% / HYDROCORTISONE 1% ) 15G HOE</t>
+          <t>VICIDE CREAM 5%  (ACYCLOVIR 15MG/G) 10G PAHANG</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
@@ -4566,16 +4566,16 @@
         </is>
       </c>
       <c r="E133" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G133" s="10" t="n">
-        <v>8.15</v>
+        <v>7.45</v>
       </c>
       <c r="H133" s="10" t="n">
-        <v>16.3</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="134">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>VICIDE CREAM 5%  (ACYCLOVIR 15MG/G) 10G PAHANG</t>
+          <t>AEVA THYMOL GARGLE 120ML APEX</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -4594,20 +4594,20 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>7.45</v>
+        <v>5.3</v>
       </c>
       <c r="H134" s="7" t="n">
-        <v>7.45</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="135">
@@ -4616,30 +4616,30 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>AEVA THYMOL GARGLE 120ML APEX</t>
+          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DRIMINATE</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E135" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G135" s="10" t="n">
-        <v>5.3</v>
+        <v>1.29</v>
       </c>
       <c r="H135" s="10" t="n">
-        <v>10.6</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="136">
@@ -4648,30 +4648,30 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
+          <t>KLORAXIN EYE OINTMENT ( CHLORAMPHENICOL 1%) 5G UNIMED</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>DRIMINATE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F136" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>1.29</v>
+        <v>2.8</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>3.87</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="137">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>KLORAXIN EYE OINTMENT ( CHLORAMPHENICOL 1%) 5G UNIMED</t>
+          <t>INJ TT VACCINE (TETANUS) 0.5ML SM PHARMA</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
@@ -4690,20 +4690,20 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>0.5ML</t>
         </is>
       </c>
       <c r="E137" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G137" s="10" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="H137" s="10" t="n">
-        <v>8.4</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="138">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>INJ TT VACCINE (TETANUS) 0.5ML SM PHARMA</t>
+          <t>INJ TYPHIM IV ( TYPHOID VACCINE ) SANOFI</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -4722,20 +4722,20 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>0.5ML</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>3.75</v>
+        <v>59</v>
       </c>
       <c r="H138" s="7" t="n">
-        <v>22.5</v>
+        <v>118</v>
       </c>
     </row>
     <row r="139">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>INJ TYPHIM IV ( TYPHOID VACCINE ) SANOFI</t>
+          <t>IBUFEN SYRUP (IBUPROFEN 100MG/ 5ML) DYNAPHARM</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
@@ -4754,20 +4754,20 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>BTL</t>
         </is>
       </c>
       <c r="E139" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G139" s="10" t="n">
-        <v>59</v>
+        <v>3.27</v>
       </c>
       <c r="H139" s="10" t="n">
-        <v>118</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="140">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>IBUFEN SYRUP (IBUPROFEN 100MG/ 5ML) DYNAPHARM</t>
+          <t>INJ PRIORIX (MMR) 0.5ML GSK</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -4786,20 +4786,20 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>BTL</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>3.27</v>
+        <v>46.7</v>
       </c>
       <c r="H140" s="7" t="n">
-        <v>3.27</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="141">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>INJ PRIORIX (MMR) 0.5ML GSK</t>
+          <t>SYR ENHANCIN (AMOXYCILLIN AND CLAVULANIC ACID 312.5MG/5ML ) 60ML RANBAXY</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
@@ -4818,20 +4818,20 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E141" s="8" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G141" s="10" t="n">
-        <v>46.7</v>
+        <v>8.4</v>
       </c>
       <c r="H141" s="10" t="n">
-        <v>46.7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="142">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>SYR ENHANCIN (AMOXYCILLIN AND CLAVULANIC ACID 312.5MG/5ML ) 60ML RANBAXY</t>
+          <t>INJ PREDON INJECTION 25MG/ML HEALOL PHARMACEUTICALS SDN. BHD.</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
@@ -4850,20 +4850,20 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>8.4</v>
+        <v>1.32</v>
       </c>
       <c r="H142" s="7" t="n">
-        <v>42</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="143">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>INJ PREDON INJECTION 25MG/ML HEALOL PHARMACEUTICALS SDN. BHD.</t>
+          <t>SYR IXIME ( CEFIXIME 100MG/5ML ) 50ML LUPIN</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
@@ -4882,20 +4882,20 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E143" s="8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F143" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G143" s="10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="H143" s="10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>SYR IXIME ( CEFIXIME 100MG/5ML ) 50ML LUPIN</t>
+          <t>XOIN (N-BUTYL-2-CYANOACRYLATE) TOPICAL SKIN ADHESIVE 0.25ML REEVAX PHARMA</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
@@ -4914,20 +4914,20 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>PEN</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H144" s="7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="145">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>XOIN (N-BUTYL-2-CYANOACRYLATE) TOPICAL SKIN ADHESIVE 0.25ML REEVAX PHARMA</t>
+          <t>MONITAZONE (MOMETASONE FUROATE) 50MCG/ACTUATION NASAL SPRAY 140MD SHAMCHUNDANG PHARM</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
@@ -4946,20 +4946,20 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>PEN</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E145" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F145" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G145" s="10" t="n">
-        <v>30</v>
+        <v>35.71429</v>
       </c>
       <c r="H145" s="10" t="n">
-        <v>60</v>
+        <v>71.43000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>MONITAZONE (MOMETASONE FUROATE) 50MCG/ACTUATION NASAL SPRAY 140MD SHAMCHUNDANG PHARM</t>
+          <t>APPETON A-Z VITAMIN C 30MG PASTILLES 5'S</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
@@ -4978,20 +4978,20 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>35.71429</v>
+        <v>0</v>
       </c>
       <c r="H146" s="7" t="n">
-        <v>71.43000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>APPETON A-Z VITAMIN C 30MG PASTILLES 5'S</t>
+          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
@@ -5010,20 +5010,20 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>AMPULE</t>
         </is>
       </c>
       <c r="E147" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F147" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G147" s="10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H147" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+          <t>KETOTOP PLASTER (KETOPROFEN) 30MG 7'S HANDOK</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
@@ -5042,80 +5042,48 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>2.5</v>
+        <v>9.021000000000001</v>
       </c>
       <c r="H148" s="7" t="n">
-        <v>5</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>KETOTOP PLASTER (KETOPROFEN) 30MG 7'S HANDOK</t>
-        </is>
-      </c>
-      <c r="C149" s="8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D149" s="8" t="inlineStr">
-        <is>
-          <t>PACKET</t>
-        </is>
-      </c>
-      <c r="E149" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="F149" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" s="10" t="n">
-        <v>9.021000000000001</v>
-      </c>
-      <c r="H149" s="10" t="n">
-        <v>9.02</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="11" t="inlineStr">
+      <c r="A149" s="11" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="H150" s="12" t="n">
+      <c r="H149" s="12" t="n">
         <v>4883.759999999999</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Total line items: 139</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Total line items: 140</t>
+          <t>Generated: 2026-06-06 15:16</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Generated: 2026-06-06 08:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="13" t="inlineStr">
+      <c r="A153" s="13" t="inlineStr">
         <is>
           <t>Note: Unit costs are from latest purchase price. Verify with supplier before confirming order.</t>
         </is>
@@ -5124,7 +5092,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A149:G149"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PO_TBD_20260606.xlsx
+++ b/PO_TBD_20260606.xlsx
@@ -700,10 +700,10 @@
         <v>30</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="13">
@@ -1020,10 +1020,10 @@
         <v>17</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -1116,10 +1116,10 @@
         <v>15</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>0</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="26">
@@ -1212,10 +1212,10 @@
         <v>2</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -1308,10 +1308,10 @@
         <v>13</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>0</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="32">
@@ -2812,10 +2812,10 @@
         <v>16</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>0</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="79">
@@ -4892,10 +4892,10 @@
         <v>3</v>
       </c>
       <c r="G143" s="10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H143" s="10" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="144">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="H149" s="12" t="n">
-        <v>4883.759999999999</v>
+        <v>5260.009999999999</v>
       </c>
     </row>
     <row r="151">
@@ -5078,7 +5078,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-06 15:16</t>
+          <t>Generated: 2026-06-06 15:34</t>
         </is>
       </c>
     </row>
